--- a/WBS/開発演習_WBS.xlsx
+++ b/WBS/開発演習_WBS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30529"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\event-application-system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nihondics.sharepoint.com/sites/AIVer1.0/Shared Documents/作業チーム/チーム開発演習_test_佐々木/event-application-system/WBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{D3131245-736F-482B-9426-83CAA6F0AA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45A4B480-9279-4DCE-A047-A37E3BBB4055}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{D3131245-736F-482B-9426-83CAA6F0AA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE557208-E0D1-4265-84F6-A48FC68EC901}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="200">
   <si>
     <t>チーム開発演習 大枠WBS（1人用・イベント申込システム）</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>DoDチェックリスト／振り返りメモ</t>
-  </si>
-  <si>
-    <t>着手中</t>
   </si>
   <si>
     <t>合計</t>
@@ -649,7 +646,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1276,8 +1273,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
@@ -1290,12 +1287,12 @@
     <col min="11" max="11" width="30" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.6" customHeight="1">
+    <row r="1" spans="1:11" ht="21.65" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1330,7 +1327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="36" customHeight="1">
+    <row r="3" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -1363,7 +1360,7 @@
       </c>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11" ht="54" customHeight="1">
+    <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -1396,7 +1393,7 @@
       </c>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="54" customHeight="1">
+    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
@@ -1429,7 +1426,7 @@
       </c>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="36" customHeight="1">
+    <row r="6" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4" t="s">
         <v>27</v>
       </c>
@@ -1462,7 +1459,7 @@
       </c>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="1:11" ht="36" customHeight="1">
+    <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1495,7 +1492,7 @@
       </c>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="1:11" ht="36" customHeight="1">
+    <row r="8" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
@@ -1528,7 +1525,7 @@
       </c>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:11" ht="36" customHeight="1">
+    <row r="9" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4" t="s">
         <v>39</v>
       </c>
@@ -1559,7 +1556,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:11" ht="36" customHeight="1">
+    <row r="10" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
         <v>44</v>
       </c>
@@ -1582,7 +1579,7 @@
         <v>0.5</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I10" s="6">
         <v>46282</v>
@@ -1590,9 +1587,9 @@
       <c r="J10" s="6"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="7">
         <f>SUM(F3:F10)</f>
@@ -1603,8 +1600,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75"/>
-    <row r="13" spans="1:11" ht="15.75"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A3:K10">
@@ -1646,8 +1641,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K50"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:K47"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
@@ -1661,29 +1656,29 @@
     <col min="11" max="11" width="28" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.6" customHeight="1">
+    <row r="1" spans="1:11" ht="21.65" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>6</v>
@@ -1701,7 +1696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8" t="s">
         <v>12</v>
       </c>
@@ -1720,21 +1715,21 @@
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:11" ht="36" customHeight="1">
+    <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>16</v>
@@ -1753,24 +1748,24 @@
       </c>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="36" customHeight="1">
+    <row r="5" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5" s="4">
         <v>2</v>
@@ -1786,24 +1781,24 @@
       </c>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="36" customHeight="1">
+    <row r="6" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="F6" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6" s="4">
         <v>2.5</v>
@@ -1819,24 +1814,24 @@
       </c>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="1:11" ht="36" customHeight="1">
+    <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" s="4">
         <v>2</v>
@@ -1852,24 +1847,24 @@
       </c>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="1:11" ht="36" customHeight="1">
+    <row r="8" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="G8" s="4">
         <v>1.5</v>
@@ -1885,7 +1880,7 @@
       </c>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:11" ht="15.75">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="8" t="s">
         <v>18</v>
       </c>
@@ -1904,21 +1899,21 @@
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
     </row>
-    <row r="10" spans="1:11" ht="36" customHeight="1">
+    <row r="10" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>12</v>
@@ -1937,24 +1932,24 @@
       </c>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:11" ht="15.75">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" s="4">
         <v>1</v>
@@ -1970,24 +1965,24 @@
       </c>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11" ht="15.75">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="F12" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G12" s="4">
         <v>1</v>
@@ -2003,24 +1998,24 @@
       </c>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:11" ht="15.75">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G13" s="4">
         <v>0.5</v>
@@ -2036,24 +2031,24 @@
       </c>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:11" ht="36" customHeight="1">
+    <row r="14" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="G14" s="4">
         <v>2.5</v>
@@ -2069,7 +2064,7 @@
       </c>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="8" t="s">
         <v>22</v>
       </c>
@@ -2088,24 +2083,24 @@
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11" ht="36" customHeight="1">
+    <row r="16" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="G16" s="4">
         <v>1.5</v>
@@ -2121,24 +2116,24 @@
       </c>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" spans="1:11" ht="15.75">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G17" s="4">
         <v>1.5</v>
@@ -2154,7 +2149,7 @@
       </c>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="36" customHeight="1">
+    <row r="18" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="8" t="s">
         <v>27</v>
       </c>
@@ -2173,21 +2168,21 @@
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" ht="36" customHeight="1">
+    <row r="19" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>22</v>
@@ -2206,21 +2201,21 @@
       </c>
       <c r="K19" s="4"/>
     </row>
-    <row r="20" spans="1:11" ht="36" customHeight="1">
+    <row r="20" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>22</v>
@@ -2239,21 +2234,21 @@
       </c>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:11" ht="36" customHeight="1">
+    <row r="21" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="E21" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>22</v>
@@ -2272,21 +2267,21 @@
       </c>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="1:11" ht="36" customHeight="1">
+    <row r="22" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>22</v>
@@ -2305,21 +2300,21 @@
       </c>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:11" ht="36" customHeight="1">
+    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>22</v>
@@ -2338,24 +2333,24 @@
       </c>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:11" ht="36" customHeight="1">
+    <row r="24" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="E24" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G24" s="4">
         <v>3</v>
@@ -2371,24 +2366,24 @@
       </c>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:11" ht="36" customHeight="1">
+    <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G25" s="4">
         <v>4</v>
@@ -2404,24 +2399,24 @@
       </c>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:11" ht="36" customHeight="1">
+    <row r="26" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="G26" s="4">
         <v>1</v>
@@ -2437,7 +2432,7 @@
       </c>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:11" ht="36" customHeight="1">
+    <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="8" t="s">
         <v>31</v>
       </c>
@@ -2456,24 +2451,24 @@
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="1:11" ht="36" customHeight="1">
+    <row r="28" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="G28" s="4">
         <v>4</v>
@@ -2489,24 +2484,24 @@
       </c>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:11" ht="36" customHeight="1">
+    <row r="29" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G29" s="4">
         <v>2</v>
@@ -2522,24 +2517,24 @@
       </c>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:11" ht="36" customHeight="1">
+    <row r="30" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="G30" s="4">
         <v>5.5</v>
@@ -2555,24 +2550,24 @@
       </c>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" spans="1:11" ht="36" customHeight="1">
+    <row r="31" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="G31" s="4">
         <v>4</v>
@@ -2588,24 +2583,24 @@
       </c>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" spans="1:11" ht="36" customHeight="1">
+    <row r="32" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="G32" s="4">
         <v>4.5</v>
@@ -2621,24 +2616,24 @@
       </c>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" spans="1:11" ht="36" customHeight="1">
+    <row r="33" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="G33" s="4">
         <v>2</v>
@@ -2654,24 +2649,24 @@
       </c>
       <c r="K33" s="4"/>
     </row>
-    <row r="34" spans="1:11" ht="36" customHeight="1">
+    <row r="34" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C34" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="F34" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G34" s="4">
         <v>1</v>
@@ -2687,7 +2682,7 @@
       </c>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="8" t="s">
         <v>35</v>
       </c>
@@ -2706,21 +2701,21 @@
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
     </row>
-    <row r="36" spans="1:11" ht="36" customHeight="1">
+    <row r="36" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="E36" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>31</v>
@@ -2739,24 +2734,24 @@
       </c>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:11" ht="15.75">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="F37" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G37" s="4">
         <v>2</v>
@@ -2772,7 +2767,7 @@
       </c>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="8" t="s">
         <v>39</v>
       </c>
@@ -2791,24 +2786,24 @@
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
     </row>
-    <row r="39" spans="1:11" ht="36" customHeight="1">
+    <row r="39" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E39" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="F39" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G39" s="4">
         <v>2.5</v>
@@ -2822,24 +2817,24 @@
       <c r="J39" s="6"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:11" ht="15.75">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>177</v>
-      </c>
       <c r="E40" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G40" s="4">
         <v>2.5</v>
@@ -2853,24 +2848,24 @@
       <c r="J40" s="6"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" spans="1:11" ht="15.75">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="F41" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G41" s="4">
         <v>1.5</v>
@@ -2884,24 +2879,24 @@
       <c r="J41" s="6"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11" ht="15.75">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C42" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="G42" s="4">
         <v>1.5</v>
@@ -2915,9 +2910,9 @@
       <c r="J42" s="6"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>45</v>
@@ -2934,21 +2929,21 @@
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" spans="1:11" ht="15.75">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>39</v>
@@ -2965,24 +2960,24 @@
       <c r="J44" s="6"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45" spans="1:11" ht="15.75">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="F45" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G45" s="4">
         <v>1</v>
@@ -2996,24 +2991,24 @@
       <c r="J45" s="6"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="1:11" ht="15.75">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>199</v>
-      </c>
       <c r="F46" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G46" s="4">
         <v>1</v>
@@ -3027,18 +3022,15 @@
       <c r="J46" s="6"/>
       <c r="K46" s="4"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="C47" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G47" s="7">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A3:A46)))*G3:G46)</f>
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15.75"/>
-    <row r="49" ht="15.75"/>
-    <row r="50" ht="15.75"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A3:K46">
@@ -3079,6 +3071,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0eb4123e-ff08-448a-a51c-d574d85865b6" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8d6e06c-e60e-47a7-a324-5df51f361a1d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010012AB853B196F794D8522E079E5062DE1" ma:contentTypeVersion="10" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f5519c8ad0001dc1944c7d5117d6ef1e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8d6e06c-e60e-47a7-a324-5df51f361a1d" xmlns:ns3="0eb4123e-ff08-448a-a51c-d574d85865b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6b6fc7ab0c5db989cb71f9aed3612649" ns2:_="" ns3:_="">
     <xsd:import namespace="e8d6e06c-e60e-47a7-a324-5df51f361a1d"/>
@@ -3267,34 +3279,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0eb4123e-ff08-448a-a51c-d574d85865b6" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8d6e06c-e60e-47a7-a324-5df51f361a1d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D291B805-DD5A-411A-AC9E-2CE043F9F335}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B8847C0-5130-4101-A4C5-741899C966B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7520B1E3-ADE6-4F00-AE17-68568CA51768}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7520B1E3-ADE6-4F00-AE17-68568CA51768}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0eb4123e-ff08-448a-a51c-d574d85865b6"/>
+    <ds:schemaRef ds:uri="e8d6e06c-e60e-47a7-a324-5df51f361a1d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B8847C0-5130-4101-A4C5-741899C966B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D291B805-DD5A-411A-AC9E-2CE043F9F335}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e8d6e06c-e60e-47a7-a324-5df51f361a1d"/>
+    <ds:schemaRef ds:uri="0eb4123e-ff08-448a-a51c-d574d85865b6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>